--- a/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20260908.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20260908.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D52"/>
+  <dimension ref="A1:D53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.75" customWidth="1" min="1" max="1"/>
@@ -611,12 +611,12 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>137,675</t>
+          <t>138,025</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>26.37%</t>
+          <t>26.73%</t>
         </is>
       </c>
     </row>
@@ -633,12 +633,12 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>99,740</t>
+          <t>99,990</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>8.48%</t>
+          <t>8.54%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>7.91%</t>
+          <t>8.01%</t>
         </is>
       </c>
     </row>
@@ -677,12 +677,12 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>50,765</t>
+          <t>50,865</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>6.08%</t>
+          <t>6.03%</t>
         </is>
       </c>
     </row>
@@ -699,12 +699,12 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>120,955</t>
+          <t>121,305</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.40%</t>
+          <t>5.35%</t>
         </is>
       </c>
     </row>
@@ -721,12 +721,12 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>59,500</t>
+          <t>59,650</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>4.50%</t>
+          <t>4.21%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.18%</t>
+          <t>3.14%</t>
         </is>
       </c>
     </row>
@@ -765,12 +765,12 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>19,695</t>
+          <t>19,825</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.15%</t>
+          <t>3.12%</t>
         </is>
       </c>
     </row>
@@ -787,12 +787,12 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>65,245</t>
+          <t>65,495</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.08%</t>
+          <t>3.06%</t>
         </is>
       </c>
     </row>
@@ -809,12 +809,12 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>44,995</t>
+          <t>45,295</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.90%</t>
+          <t>2.89%</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>18,283</t>
+          <t>18,383</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.73%</t>
+          <t>2.75%</t>
         </is>
       </c>
     </row>
@@ -853,12 +853,12 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>76,745</t>
+          <t>76,895</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.14%</t>
+          <t>2.26%</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.09%</t>
+          <t>2.07%</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.04%</t>
+          <t>2.02%</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.79%</t>
+          <t>1.77%</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.56%</t>
+          <t>1.55%</t>
         </is>
       </c>
     </row>
@@ -968,51 +968,51 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.52%</t>
+          <t>1.51%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>XEL US</t>
+          <t>NBIS US</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Xcel 能源</t>
+          <t>尼比厄斯集團公眾有限公司</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>36,050</t>
+          <t>11,681</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.46%</t>
+          <t>1.50%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>NBIS US</t>
+          <t>XEL US</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>尼比厄斯集團公眾有限公司</t>
+          <t>Xcel 能源</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>11,681</t>
+          <t>36,050</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.42%</t>
+          <t>1.46%</t>
         </is>
       </c>
     </row>
@@ -1034,139 +1034,139 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.38%</t>
+          <t>1.37%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>ALAB US</t>
+          <t>ED US</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>Astera實驗室公司</t>
+          <t>聯合愛迪生</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>7,990</t>
+          <t>21,308</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.33%</t>
+          <t>1.21%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>ED US</t>
+          <t>ALAB US</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>聯合愛迪生</t>
+          <t>Astera實驗室公司</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>21,308</t>
+          <t>7,990</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.22%</t>
+          <t>1.21%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>WEC US</t>
+          <t>C_NTD</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>WEC能源集團公司</t>
+          <t>CASH</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>18,355</t>
+          <t>64,480,456</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.04%</t>
+          <t>1.07%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>PCG US</t>
+          <t>CRWV US</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>太平洋電力瓦斯公司</t>
+          <t>CoreWeave Inc</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>125,985</t>
+          <t>19,587</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>0.96%</t>
+          <t>1.03%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>CRWV US</t>
+          <t>WEC US</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>CoreWeave Inc</t>
+          <t>WEC能源集團公司</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>19,587</t>
+          <t>18,355</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>0.94%</t>
+          <t>1.03%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>C_NTD</t>
+          <t>PCG US</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>CASH</t>
+          <t>太平洋電力瓦斯公司</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>53,750,456</t>
+          <t>125,985</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>0.91%</t>
+          <t>0.98%</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.90%</t>
+          <t>0.89%</t>
         </is>
       </c>
     </row>
@@ -1210,46 +1210,46 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.88%</t>
+          <t>0.85%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>PPL US</t>
+          <t>CNP US</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>PPL Corp</t>
+          <t>Centerpoint能源</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>42,930</t>
+          <t>37,340</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.81%</t>
+          <t>0.79%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>CNP US</t>
+          <t>PPL US</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>Centerpoint能源</t>
+          <t>PPL Corp</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>37,340</t>
+          <t>42,930</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -1276,7 +1276,7 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.75%</t>
+          <t>0.74%</t>
         </is>
       </c>
     </row>
@@ -1298,7 +1298,29 @@
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.21%</t>
+          <t>0.20%</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>RDI_USD</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>RECEIVABLES FOR DISPOSAL OF INVESTMENTS</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>23,655</t>
+        </is>
+      </c>
+      <c r="D53" s="4" t="inlineStr">
+        <is>
+          <t>0.00%</t>
         </is>
       </c>
     </row>
